--- a/data/trans_camb/P1401-Estudios-trans_camb.xlsx
+++ b/data/trans_camb/P1401-Estudios-trans_camb.xlsx
@@ -598,27 +598,27 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
+          <t>1,13</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>-0,05</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>1,46</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>-0,03</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
           <t>1,33</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>-0,05</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>1,46</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>-0,03</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>1,42</t>
         </is>
       </c>
     </row>
@@ -631,32 +631,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-1,22; 1,26</t>
+          <t>-1,37; 1,36</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-0,23; 2,89</t>
+          <t>-0,46; 2,42</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-1,42; 1,64</t>
+          <t>-1,47; 1,47</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-0,03; 2,78</t>
+          <t>-0,07; 2,85</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-1,09; 1,02</t>
+          <t>-0,97; 1,0</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,41; 2,47</t>
+          <t>0,34; 2,37</t>
         </is>
       </c>
     </row>
@@ -674,7 +674,7 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>73,7%</t>
+          <t>62,63%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>51,27%</t>
+          <t>51,32%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -694,7 +694,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>59,14%</t>
+          <t>55,4%</t>
         </is>
       </c>
     </row>
@@ -707,32 +707,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-51,67; 104,41</t>
+          <t>-56,0; 119,26</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-12,71; 234,1</t>
+          <t>-22,41; 196,14</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-42,25; 69,58</t>
+          <t>-43,73; 70,22</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-0,79; 132,81</t>
+          <t>-2,81; 133,85</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-39,04; 51,58</t>
+          <t>-34,56; 47,44</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>12,79; 125,45</t>
+          <t>9,36; 123,5</t>
         </is>
       </c>
     </row>
@@ -754,7 +754,7 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>0,61</t>
+          <t>0,76</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -764,7 +764,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>-0,05</t>
+          <t>0,13</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -774,7 +774,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>0,3</t>
+          <t>0,46</t>
         </is>
       </c>
     </row>
@@ -787,32 +787,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-0,94; 0,17</t>
+          <t>-0,94; 0,19</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-0,06; 1,37</t>
+          <t>0,02; 1,47</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-1,29; 0,36</t>
+          <t>-1,19; 0,48</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-1,06; 0,69</t>
+          <t>-0,73; 0,84</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-0,9; 0,13</t>
+          <t>-0,84; 0,19</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-0,25; 0,83</t>
+          <t>-0,06; 0,98</t>
         </is>
       </c>
     </row>
@@ -830,7 +830,7 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>62,04%</t>
+          <t>76,78%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -840,7 +840,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>-2,81%</t>
+          <t>7,65%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -850,7 +850,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>23,15%</t>
+          <t>35,37%</t>
         </is>
       </c>
     </row>
@@ -863,32 +863,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-70,53; 24,77</t>
+          <t>-68,53; 37,71</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-7,23; 196,05</t>
+          <t>-0,65; 217,82</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-57,67; 32,31</t>
+          <t>-55,42; 41,96</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-46,02; 55,61</t>
+          <t>-32,47; 71,59</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-55,51; 10,96</t>
+          <t>-53,84; 19,91</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-15,08; 83,32</t>
+          <t>-3,67; 97,62</t>
         </is>
       </c>
     </row>
@@ -910,7 +910,7 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>2,05</t>
+          <t>2,18</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
@@ -920,7 +920,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>0,48</t>
+          <t>0,51</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -930,7 +930,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>1,27</t>
+          <t>1,34</t>
         </is>
       </c>
     </row>
@@ -943,32 +943,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-0,94; 0,8</t>
+          <t>-0,82; 0,82</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,89; 3,37</t>
+          <t>1,04; 3,57</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,56; 4,25</t>
+          <t>0,63; 4,21</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-0,81; 1,57</t>
+          <t>-0,88; 1,45</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,18; 2,13</t>
+          <t>0,19; 2,04</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,39; 2,06</t>
+          <t>0,51; 2,18</t>
         </is>
       </c>
     </row>
@@ -986,7 +986,7 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>466,33%</t>
+          <t>495,13%</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
@@ -996,7 +996,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>51,38%</t>
+          <t>54,14%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1006,7 +1006,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>185,26%</t>
+          <t>195,86%</t>
         </is>
       </c>
     </row>
@@ -1024,27 +1024,27 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>44,26; —</t>
+          <t>43,69; —</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>4,27; 1328,69</t>
+          <t>9,67; 1123,51</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-54,21; 494,64</t>
+          <t>-58,98; 491,81</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0,79; 678,42</t>
+          <t>2,65; 663,5</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>11,98; 720,75</t>
+          <t>25,07; 642,72</t>
         </is>
       </c>
     </row>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>0,85</t>
+          <t>0,98</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -1076,7 +1076,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>0,12</t>
+          <t>0,26</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1086,7 +1086,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,48</t>
+          <t>0,61</t>
         </is>
       </c>
     </row>
@@ -1099,32 +1099,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-0,72; 0,24</t>
+          <t>-0,77; 0,25</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,21; 1,44</t>
+          <t>0,43; 1,55</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-0,71; 0,68</t>
+          <t>-0,73; 0,71</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-0,56; 0,73</t>
+          <t>-0,44; 0,84</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-0,54; 0,32</t>
+          <t>-0,56; 0,33</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,01; 0,96</t>
+          <t>0,21; 1,03</t>
         </is>
       </c>
     </row>
@@ -1142,7 +1142,7 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>74,55%</t>
+          <t>85,19%</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
@@ -1152,7 +1152,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>5,96%</t>
+          <t>12,98%</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>30,25%</t>
+          <t>38,56%</t>
         </is>
       </c>
     </row>
@@ -1175,32 +1175,32 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-51,88; 26,38</t>
+          <t>-52,85; 32,42</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>15,35; 160,26</t>
+          <t>26,83; 176,42</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-30,6; 44,07</t>
+          <t>-31,04; 40,91</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-24,76; 45,57</t>
+          <t>-18,76; 52,0</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-29,78; 24,47</t>
+          <t>-30,81; 25,01</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>1,06; 70,58</t>
+          <t>11,35; 76,64</t>
         </is>
       </c>
     </row>
